--- a/sheet/통합시트_예시.xlsx
+++ b/sheet/통합시트_예시.xlsx
@@ -15,23 +15,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공유캠퍼스" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="거점형 선택 교육과정" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과목소개" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_선택군" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_규칙" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_과목데이터" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_편제표" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_직업데이터" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업데이터" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_선택군" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_규칙" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_과목데이터" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_편제표" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_선택군" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_규칙" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_과목데이터" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_편제표" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_직업데이터" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_선택군" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_규칙" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_과목데이터" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_편제표" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_직업데이터" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_규칙작성법" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_2026_조건(참고)" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_선택군" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_규칙" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_과목데이터" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_편제표" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_규칙작성법" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_2026_조건(참고)" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -656,17 +654,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>공유캠퍼스</t>
+          <t>직업데이터</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>운영 학교와 학기별 과목 (과목 카드에 학교명 표시)</t>
+          <t>직업별 관련 과목 (현재 웹페이지에서는 사용하지 않음)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>매 학년도 초 확인</t>
+          <t>필요할 때만 수정</t>
         </is>
       </c>
     </row>
@@ -678,12 +676,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>거점형 선택 교육과정</t>
+          <t>공유캠퍼스</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>거점학교 개설 과목 안내 (보관용)</t>
+          <t>운영 학교와 학기별 과목 (과목 카드에 학교명 표시)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -695,22 +693,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>🟦 학년별</t>
+          <t>🟩 공통</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2027_선택군</t>
+          <t>거점형 선택 교육과정</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>선택군(A~K): 학기, 몇 과목 선택, 학점, 공유캠퍼스 여부</t>
+          <t>거점학교 개설 과목 안내 (보관용)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>새 입학년도: 작년 탭 복사 후 수정</t>
+          <t>매 학년도 초 확인</t>
         </is>
       </c>
     </row>
@@ -722,12 +720,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2027_규칙</t>
+          <t>2027_선택군</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>수강신청 조건 (예전 [조건] 탭을 대신함). 작성법은 _규칙작성법 탭</t>
+          <t>선택군(A~K): 학기, 몇 과목 선택, 학점, 공유캠퍼스 여부</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -744,12 +742,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>2027_과목데이터</t>
+          <t>2027_규칙</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>학년마다 다른 것만: 과목명, 편성(예: 2학년 2A군(2학년 1학기) 선택), 학점, 교과군, 선택유형, 평가, 수능출제</t>
+          <t>수강신청 조건 (예전 [조건] 탭을 대신함). 작성법은 _규칙작성법 탭</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -766,17 +764,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2027_편제표</t>
+          <t>2027_과목데이터</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>학점 배당표 (편제표 화면에 그대로 표시)</t>
+          <t>학년마다 다른 것만: 과목명, 편성(예: 2학년 2A군(2학년 1학기) 선택), 학점, 교과군, 선택유형, 평가, 수능출제</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>새 입학년도: 확정 편제표 붙여 넣기</t>
+          <t>새 입학년도: 작년 탭 복사 후 수정</t>
         </is>
       </c>
     </row>
@@ -788,17 +786,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>2027_직업데이터</t>
+          <t>2027_편제표</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>직업별 관련 과목 (현재 웹페이지에서는 사용하지 않음)</t>
+          <t>학점 배당표 (편제표 화면에 그대로 표시)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>새 입학년도: 확정 편제표 붙여 넣기</t>
         </is>
       </c>
     </row>
@@ -835,11 +833,11 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>① 작년 학년별 탭 5개를 복사 → 이름 앞 연도를 새 연도로 변경 (예: 2028_과목데이터)
+          <t>① 작년 학년별 탭 4개를 복사 → 이름 앞 연도를 새 연도로 변경 (예: 2028_과목데이터)
 ② 기본정보에 새 연도 열 추가 (학생공개는 X로 시작)
 ③ 내용 수정 후 웹페이지 주소에 ?year=2028&amp;check=1 을 붙여 점검
 ④ 문제가 없으면 학생공개를 O로 바꾸기
-⑤ 졸업한 학년의 탭 5개와 기본정보 열 삭제</t>
+⑤ 졸업한 학년의 탭 4개와 기본정보 열 삭제</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -882,6 +880,409 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001D4ED8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>군ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>표시이름</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>학기</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>선택과목수</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>학점</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>희망자선택</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>공유캠퍼스</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>안내문</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2D</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>공유캠퍼스(금요일 또는 주말 운영)는 희망자에 한해 모집시기(3월초)에 해당 학교에 시험이나 면접을 본 후 합격자만 수강이 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>공유캠퍼스(금요일 또는 주말 운영)는 희망자에 한해 모집시기(3월초)에 해당 학교에 시험이나 면접을 본 후 합격자만 수강이 가능합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>3C</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>3D</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>3E</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001D4ED8"/>
@@ -1368,7 +1769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001D4ED8"/>
@@ -6419,7 +6820,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001D4ED8"/>
@@ -10665,649 +11066,6 @@
       <c r="Q122" s="2" t="inlineStr"/>
       <c r="R122" s="2" t="inlineStr"/>
       <c r="S122" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001D4ED8"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>직업</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>휘경여고 개설 필요(관련) 과목</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>가수/성악가/연주가</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>음악, 음악 감상과 비평, 음악과 미디어</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>간호사/보건교사</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>화학, 생명과학, 물질과 에너지, 화학 반응의 세계, 세포와 물질대사, 생물의 유전</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>감정평가사</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>경제 수학, 세계사, 한국지리 탐구, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 법과 사회, 경제, 금융과 경제생활, 인간과 경제활동</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>건축가/건축기사</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>대수, 기하, 직무 수학, 도시의 미래 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>검사/판사/변호사</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 직무 의사소통, 독서 토론과 글쓰기, 언어생활 탐구, 정치, 법과 사회</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>게임 기획자/개발자/시나리오 작가</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>수학과 문화, 문학과 영상, 정보, 인공지능 기초, 인간과 심리</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>경영/마케팅/홍보 전문가</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 직무 의사소통, 독서 토론과 글쓰기, 매체 의사소통, 언어생활 탐구, 직무 수학, 현대사회와 윤리, 경제, 윤리와 사상, 인문학과 윤리, 윤리문제 탐구, 인간과 경제활동</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>공무원(행정, 통계, 기술 등)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>직무 의사소통, 직무 수학, 수학과 문화, 세계사, 도시의 미래 탐구, 한국지리 탐구, 정치, 사회문제 탐구, 기후변화와 지속가능한 세계, 법과 사회, 인간과 경제활동</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>관광통역안내원/여행 안내원</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>영어 독해와 작문, 영어II, 실생활 영어 회화, 미디어 영어, 제2외국어 과목 전반 (일본어, 중국어, 일본어 회화, 중국어 회화, 일본 문화, 중국 문화 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>교육 연구원/교육학자</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>주제 탐구 독서, 교육의 이해</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>국어 교사/언어학자</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 문학, 주제 탐구 독서, 독서 토론과 글쓰기, 언어생활 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>국제/외교 전문가(외교관 등)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>영어Ⅰ, 영어 발표와 토론, 심화 영어, 세계사, 세계시민과 지리, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 정치</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>기계/로봇 공학자</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 기하, 물리학, 역학과 에너지, 융합과학 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>기자/언론인(방송/신문)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 문학, 주제 탐구 독서, 독서 토론과 글쓰기, 매체 의사소통, 언어생활 탐구, 영미 문학 읽기, 직무 영어, 세계 문화와 영어, 세계사, 세계시민과 지리, 도시의 미래 탐구, 한국지리 탐구, 정치, 사회문제 탐구, 기후변화와 지속가능한 세계, 인간과 철학, 논리와 사고, 인간과 심리, 삶과 종교, 제2외국어 및 한문 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>노무사</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>직무 의사소통, 법과 사회</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>논술지도사</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>독서 토론과 글쓰기, 논리와 사고</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>데이터 과학자/분석가</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>확률과 통계, 인공지능 수학, 직무 수학, 융합과학 탐구, 정보</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>도시 계획가/도시연구원</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>수학과 문화, 도시의 미래 탐구, 한국지리 탐구, 생태와 환경</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>무역 종사자</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>영어Ⅰ, 영어 독해와 작문, 영어II, 직무 영어, 미디어 영어, 세계 문화와 영어, 세계시민과 지리, 경제, 인간과 경제활동, 제2외국어 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>문헌정보학자/사서</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>독서와 작문, 문학, 주제 탐구 독서, 언어생활 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>물리치료사/재활 관련</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>운동과 건강, 생명과학, 세포와 물질대사</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>물리학자</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 물리학, 역학과 에너지, 전자기와 양자</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>미술/디자인 전문가(시각/산업 디자이너 등)</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>기하, 수학과 문화, 미술, 미술 감상과 비평, 미술과 매체</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>방송 PD/연출가</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>매체 의사소통, 문학, 문학과 영상, 영미 문학 읽기, 세계 문화와 영어, 세계시민과 지리, 사회와 문화, 역사로 탐구하는 현대 세계, 기후변화와 지속가능한 세계, 사회문제 탐구, 삶과 종교</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>번역가/통역가</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>독서와 작문, 직무 영어, 영어 독해와 작문, 심화 영어 독해와 작문, 심화 영어, 실생활 영어 회화, 세계 문화와 영어, 제2외국어 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>변리사</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>법과 사회, 생태와 환경</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>보험계리사/손해사정사</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>확률과 통계, 경제 수학, 법과 사회, 금융과 경제생활</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>보육교사/유치원교사</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>교육의 이해, 인간과 심리</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>사회과학연구원/사회학자</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>세계시민과 지리, 사회와 문화, 도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 인간과 심리</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>사회복지사</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>법과 사회, 도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 윤리문제 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>생명과학자/연구원</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 생명과학, 세포와 물질대사, 생물의 유전, 융합과학 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>세무사/회계사</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>경제 수학, 직무 수학, 경제, 금융과 경제생활, 인간과 경제활동</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발자/프로그래머</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>인공지능 수학, 정보, 인공지능 기초</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>수의사</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>생명과학, 세포와 물질대사, 생물의 유전</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>수학자</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 확률과 통계, 기하</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>심리/상담 전문가(놀이치료사 등)</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>인간과 심리</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>아나운서/방송 진행자</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 직무 의사소통, 매체 의사소통, 영미 문학 읽기, 세계 문화와 영어</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>약사</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>화학, 생명과학, 물질과 에너지, 화학 반응의 세계, 세포와 물질대사, 생물의 유전</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>역사학자/학예사/큐레이터</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>영미 문학 읽기, 세계사, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 한문 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>에너지/환경 기술자</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>대수, 기후변화와 지속가능한 세계, 생태와 환경, 기후변화와 환경생태</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>연극 배우/연출가/기획자</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>문학과 영상, 삶과 종교</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>작곡가/음향전문가</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>대수, 수학과 문화, 음악, 음악 감상과 비평, 음악과 미디어</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>작가(소설가/시인/에세이스트)</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 문학, 문학과 영상, 독서 토론과 글쓰기, 영어Ⅱ, 영미 문학 읽기, 미디어 영어, 세계사, 현대사회와 윤리, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 기후변화와 지속가능한 세계, 인간과 철학, 제2외국어 및 한문 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>전기전자공학자</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 기하, 전자기와 양자, 융합과학 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>정치인/정치학연구원</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 정치</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>철학/인문학 연구원</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>주제 탐구 독서, 언어생활 탐구, 세계사, 현대사회와 윤리, 윤리와 사상, 인문학과 윤리, 인간과 철학, 논리와 사고</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>천문/기상학자</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>대수, 확률과 통계, 융합과학 탐구, 지구과학, 행성우주과학</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>체육/스포츠 전문가(코치/트레이너 등)</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>체육1, 체육2, 운동과 건강, 스포츠 문화, 스포츠 과학, 스포츠 생활1, 스포츠 생활2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>통계학자/통계청 공무원</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 확률과 통계, 미적분 II, 직무 수학, 수학과 문화, 실용 통계</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>항공우주공학자</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>대수, 기하, 물리학, 역학과 에너지</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>화학공학자/신소재 연구원</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 화학, 물질과 에너지, 화학 반응의 세계, 융합과학 탐구</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21848,649 +21606,6 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="003B82F6"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>직업</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>휘경여고 개설 필요(관련) 과목</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>가수/성악가/연주가</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>음악, 음악 감상과 비평, 음악과 미디어</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>간호사/보건교사</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>화학, 생명과학, 물질과 에너지, 화학 반응의 세계, 세포와 물질대사, 생물의 유전</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>감정평가사</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>경제 수학, 세계사, 한국지리 탐구, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 법과 사회, 경제, 금융과 경제생활, 인간과 경제활동</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>건축가/건축기사</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>대수, 기하, 직무 수학, 도시의 미래 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>검사/판사/변호사</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 직무 의사소통, 독서 토론과 글쓰기, 언어생활 탐구, 정치, 법과 사회</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>게임 기획자/개발자/시나리오 작가</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>수학과 문화, 문학과 영상, 정보, 인공지능 기초, 인간과 심리</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>경영/마케팅/홍보 전문가</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 직무 의사소통, 독서 토론과 글쓰기, 매체 의사소통, 언어생활 탐구, 직무 수학, 현대사회와 윤리, 경제, 윤리와 사상, 인문학과 윤리, 윤리문제 탐구, 인간과 경제활동</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>공무원(행정, 통계, 기술 등)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>직무 의사소통, 직무 수학, 수학과 문화, 세계사, 도시의 미래 탐구, 한국지리 탐구, 정치, 사회문제 탐구, 기후변화와 지속가능한 세계, 법과 사회, 인간과 경제활동</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>관광통역안내원/여행 안내원</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>영어 독해와 작문, 영어II, 실생활 영어 회화, 미디어 영어, 제2외국어 과목 전반 (일본어, 중국어, 일본어 회화, 중국어 회화, 일본 문화, 중국 문화 등)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>교육 연구원/교육학자</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>주제 탐구 독서, 교육의 이해</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>국어 교사/언어학자</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 문학, 주제 탐구 독서, 독서 토론과 글쓰기, 언어생활 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>국제/외교 전문가(외교관 등)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>영어Ⅰ, 영어 발표와 토론, 심화 영어, 세계사, 세계시민과 지리, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 정치</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>기계/로봇 공학자</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 기하, 물리학, 역학과 에너지, 융합과학 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>기자/언론인(방송/신문)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 문학, 주제 탐구 독서, 독서 토론과 글쓰기, 매체 의사소통, 언어생활 탐구, 영미 문학 읽기, 직무 영어, 세계 문화와 영어, 세계사, 세계시민과 지리, 도시의 미래 탐구, 한국지리 탐구, 정치, 사회문제 탐구, 기후변화와 지속가능한 세계, 인간과 철학, 논리와 사고, 인간과 심리, 삶과 종교, 제2외국어 및 한문 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>노무사</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>직무 의사소통, 법과 사회</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>논술지도사</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>독서 토론과 글쓰기, 논리와 사고</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>데이터 과학자/분석가</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>확률과 통계, 인공지능 수학, 직무 수학, 융합과학 탐구, 정보</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>도시 계획가/도시연구원</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>수학과 문화, 도시의 미래 탐구, 한국지리 탐구, 생태와 환경</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>무역 종사자</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>영어Ⅰ, 영어 독해와 작문, 영어II, 직무 영어, 미디어 영어, 세계 문화와 영어, 세계시민과 지리, 경제, 인간과 경제활동, 제2외국어 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>문헌정보학자/사서</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>독서와 작문, 문학, 주제 탐구 독서, 언어생활 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>물리치료사/재활 관련</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>운동과 건강, 생명과학, 세포와 물질대사</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>물리학자</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 물리학, 역학과 에너지, 전자기와 양자</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>미술/디자인 전문가(시각/산업 디자이너 등)</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>기하, 수학과 문화, 미술, 미술 감상과 비평, 미술과 매체</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>방송 PD/연출가</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>매체 의사소통, 문학, 문학과 영상, 영미 문학 읽기, 세계 문화와 영어, 세계시민과 지리, 사회와 문화, 역사로 탐구하는 현대 세계, 기후변화와 지속가능한 세계, 사회문제 탐구, 삶과 종교</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>번역가/통역가</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>독서와 작문, 직무 영어, 영어 독해와 작문, 심화 영어 독해와 작문, 심화 영어, 실생활 영어 회화, 세계 문화와 영어, 제2외국어 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>변리사</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>법과 사회, 생태와 환경</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>보험계리사/손해사정사</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>확률과 통계, 경제 수학, 법과 사회, 금융과 경제생활</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>보육교사/유치원교사</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>교육의 이해, 인간과 심리</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>사회과학연구원/사회학자</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>세계시민과 지리, 사회와 문화, 도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 인간과 심리</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>사회복지사</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>법과 사회, 도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 윤리문제 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>생명과학자/연구원</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 생명과학, 세포와 물질대사, 생물의 유전, 융합과학 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>세무사/회계사</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>경제 수학, 직무 수학, 경제, 금융과 경제생활, 인간과 경제활동</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발자/프로그래머</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>인공지능 수학, 정보, 인공지능 기초</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>수의사</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>생명과학, 세포와 물질대사, 생물의 유전</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>수학자</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 확률과 통계, 기하</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>심리/상담 전문가(놀이치료사 등)</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>인간과 심리</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>아나운서/방송 진행자</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 직무 의사소통, 매체 의사소통, 영미 문학 읽기, 세계 문화와 영어</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>약사</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>화학, 생명과학, 물질과 에너지, 화학 반응의 세계, 세포와 물질대사, 생물의 유전</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>역사학자/학예사/큐레이터</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>영미 문학 읽기, 세계사, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 한문 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>에너지/환경 기술자</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>대수, 기후변화와 지속가능한 세계, 생태와 환경, 기후변화와 환경생태</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>연극 배우/연출가/기획자</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>문학과 영상, 삶과 종교</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>작곡가/음향전문가</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>대수, 수학과 문화, 음악, 음악 감상과 비평, 음악과 미디어</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>작가(소설가/시인/에세이스트)</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 독서와 작문, 문학, 문학과 영상, 독서 토론과 글쓰기, 영어Ⅱ, 영미 문학 읽기, 미디어 영어, 세계사, 현대사회와 윤리, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 기후변화와 지속가능한 세계, 인간과 철학, 제2외국어 및 한문 과목 전반</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>전기전자공학자</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 기하, 전자기와 양자, 융합과학 탐구</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>정치인/정치학연구원</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>화법과 언어, 정치</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>철학/인문학 연구원</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>주제 탐구 독서, 언어생활 탐구, 세계사, 현대사회와 윤리, 윤리와 사상, 인문학과 윤리, 인간과 철학, 논리와 사고</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>천문/기상학자</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>대수, 확률과 통계, 융합과학 탐구, 지구과학, 행성우주과학</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>체육/스포츠 전문가(코치/트레이너 등)</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>체육1, 체육2, 운동과 건강, 스포츠 문화, 스포츠 과학, 스포츠 생활1, 스포츠 생활2</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>통계학자/통계청 공무원</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 확률과 통계, 미적분 II, 직무 수학, 수학과 문화, 실용 통계</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>항공우주공학자</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>대수, 기하, 물리학, 역학과 에너지</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>화학공학자/신소재 연구원</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>대수, 미적분 I, 미적분 II, 화학, 물질과 에너지, 화학 반응의 세계, 융합과학 탐구</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <tabColor rgb="0093C5FD"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -22555,250 +21670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>학생공개</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>O = 학생 입학년도 목록에 보임 / X = 숨김 (주소에 ?year=2027 을 붙이면 선생님은 미리보기 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>운영과정</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>일반, 과학중점</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>일반, 과학중점</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>"일반"만 적으면 과학중점 과정 선택이 화면에서 사라지고 일반 과정으로 고정됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>학교명</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>휘경여자고등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>휘경여자고등학교</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>휘경여자고등학교</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>보고서 제목 등에 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>학교약칭</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>휘경여고</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>휘경여고</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>휘경여고</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>"휘경여고 편제표" 등에 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>수능년도</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>"29수능 출제" 표시에 사용 (입학년도 + 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>학기별교과학점</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>편제표에서 학기 합계가 이 학점 이상이면 파란색</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>자료출처</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2025학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2026학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2027학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>화면 상단 자료출처 문구</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:Z2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"O,X"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0093C5FD"/>
@@ -22903,7 +21775,250 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>학생공개</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>O = 학생 입학년도 목록에 보임 / X = 숨김 (주소에 ?year=2027 을 붙이면 선생님은 미리보기 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>운영과정</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>일반, 과학중점</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>일반, 과학중점</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"일반"만 적으면 과학중점 과정 선택이 화면에서 사라지고 일반 과정으로 고정됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>학교명</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>휘경여자고등학교</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>휘경여자고등학교</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>휘경여자고등학교</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>보고서 제목 등에 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>학교약칭</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>휘경여고</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>휘경여고</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>휘경여고</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"휘경여고 편제표" 등에 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>수능년도</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>"29수능 출제" 표시에 사용 (입학년도 + 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>학기별교과학점</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>편제표에서 학기 합계가 이 학점 이상이면 파란색</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>자료출처</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2025학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2027학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>화면 상단 자료출처 문구</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:Z2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"O,X"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0093C5FD"/>
@@ -22970,7 +22085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0093C5FD"/>
@@ -22995,38 +22110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0093C5FD"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>직업</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>휘경여고 개설 필요(관련) 과목</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>
@@ -23286,7 +22370,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>
@@ -51074,400 +50158,640 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001D4ED8"/>
+    <tabColor rgb="0016A34A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>군ID</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>표시이름</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>학기</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>선택과목수</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>학점</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>희망자선택</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>공유캠퍼스</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>안내문</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>직업</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>휘경여고 개설 필요(관련) 과목</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>가수/성악가/연주가</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+          <t>음악, 음악 감상과 비평, 음악과 미디어</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>간호사/보건교사</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+          <t>화학, 생명과학, 물질과 에너지, 화학 반응의 세계, 세포와 물질대사, 생물의 유전</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>감정평가사</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>경제 수학, 세계사, 한국지리 탐구, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 법과 사회, 경제, 금융과 경제생활, 인간과 경제활동</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2D</t>
+          <t>건축가/건축기사</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+          <t>대수, 기하, 직무 수학, 도시의 미래 탐구</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2E</t>
+          <t>검사/판사/변호사</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>공유캠퍼스(금요일 또는 주말 운영)는 희망자에 한해 모집시기(3월초)에 해당 학교에 시험이나 면접을 본 후 합격자만 수강이 가능합니다.</t>
+          <t>화법과 언어, 독서와 작문, 직무 의사소통, 독서 토론과 글쓰기, 언어생활 탐구, 정치, 법과 사회</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2F</t>
+          <t>게임 기획자/개발자/시나리오 작가</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>공유캠퍼스(금요일 또는 주말 운영)는 희망자에 한해 모집시기(3월초)에 해당 학교에 시험이나 면접을 본 후 합격자만 수강이 가능합니다.</t>
+          <t>수학과 문화, 문학과 영상, 정보, 인공지능 기초, 인간과 심리</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>경영/마케팅/홍보 전문가</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+          <t>화법과 언어, 독서와 작문, 직무 의사소통, 독서 토론과 글쓰기, 매체 의사소통, 언어생활 탐구, 직무 수학, 현대사회와 윤리, 경제, 윤리와 사상, 인문학과 윤리, 윤리문제 탐구, 인간과 경제활동</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>공무원(행정, 통계, 기술 등)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+          <t>직무 의사소통, 직무 수학, 수학과 문화, 세계사, 도시의 미래 탐구, 한국지리 탐구, 정치, 사회문제 탐구, 기후변화와 지속가능한 세계, 법과 사회, 인간과 경제활동</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3C</t>
+          <t>관광통역안내원/여행 안내원</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>영어 독해와 작문, 영어II, 실생활 영어 회화, 미디어 영어, 제2외국어 과목 전반 (일본어, 중국어, 일본어 회화, 중국어 회화, 일본 문화, 중국 문화 등)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>3D</t>
+          <t>교육 연구원/교육학자</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>주제 탐구 독서, 교육의 이해</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>3E</t>
+          <t>국어 교사/언어학자</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>화법과 언어, 독서와 작문, 문학, 주제 탐구 독서, 독서 토론과 글쓰기, 언어생활 탐구</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>3F</t>
+          <t>국제/외교 전문가(외교관 등)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>영어Ⅰ, 영어 발표와 토론, 심화 영어, 세계사, 세계시민과 지리, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 정치</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>기계/로봇 공학자</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>대수, 미적분 I, 미적분 II, 기하, 물리학, 역학과 에너지, 융합과학 탐구</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>기자/언론인(방송/신문)</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어, 독서와 작문, 문학, 주제 탐구 독서, 독서 토론과 글쓰기, 매체 의사소통, 언어생활 탐구, 영미 문학 읽기, 직무 영어, 세계 문화와 영어, 세계사, 세계시민과 지리, 도시의 미래 탐구, 한국지리 탐구, 정치, 사회문제 탐구, 기후변화와 지속가능한 세계, 인간과 철학, 논리와 사고, 인간과 심리, 삶과 종교, 제2외국어 및 한문 과목 전반</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>노무사</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>직무 의사소통, 법과 사회</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>논술지도사</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>독서 토론과 글쓰기, 논리와 사고</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>데이터 과학자/분석가</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>확률과 통계, 인공지능 수학, 직무 수학, 융합과학 탐구, 정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>도시 계획가/도시연구원</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>수학과 문화, 도시의 미래 탐구, 한국지리 탐구, 생태와 환경</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>무역 종사자</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>영어Ⅰ, 영어 독해와 작문, 영어II, 직무 영어, 미디어 영어, 세계 문화와 영어, 세계시민과 지리, 경제, 인간과 경제활동, 제2외국어 과목 전반</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>문헌정보학자/사서</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>독서와 작문, 문학, 주제 탐구 독서, 언어생활 탐구</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>물리치료사/재활 관련</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>운동과 건강, 생명과학, 세포와 물질대사</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>물리학자</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>대수, 미적분 I, 미적분 II, 물리학, 역학과 에너지, 전자기와 양자</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>미술/디자인 전문가(시각/산업 디자이너 등)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>기하, 수학과 문화, 미술, 미술 감상과 비평, 미술과 매체</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>방송 PD/연출가</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>매체 의사소통, 문학, 문학과 영상, 영미 문학 읽기, 세계 문화와 영어, 세계시민과 지리, 사회와 문화, 역사로 탐구하는 현대 세계, 기후변화와 지속가능한 세계, 사회문제 탐구, 삶과 종교</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>번역가/통역가</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>독서와 작문, 직무 영어, 영어 독해와 작문, 심화 영어 독해와 작문, 심화 영어, 실생활 영어 회화, 세계 문화와 영어, 제2외국어 과목 전반</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>변리사</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>법과 사회, 생태와 환경</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>보험계리사/손해사정사</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>확률과 통계, 경제 수학, 법과 사회, 금융과 경제생활</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>보육교사/유치원교사</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>교육의 이해, 인간과 심리</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>사회과학연구원/사회학자</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>세계시민과 지리, 사회와 문화, 도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 인간과 심리</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>사회복지사</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>법과 사회, 도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 윤리문제 탐구</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>생명과학자/연구원</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>대수, 미적분 I, 미적분 II, 생명과학, 세포와 물질대사, 생물의 유전, 융합과학 탐구</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>세무사/회계사</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>경제 수학, 직무 수학, 경제, 금융과 경제생활, 인간과 경제활동</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>소프트웨어 개발자/프로그래머</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>인공지능 수학, 정보, 인공지능 기초</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>수의사</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>생명과학, 세포와 물질대사, 생물의 유전</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>수학자</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>대수, 미적분 I, 미적분 II, 확률과 통계, 기하</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>심리/상담 전문가(놀이치료사 등)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>인간과 심리</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>아나운서/방송 진행자</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어, 직무 의사소통, 매체 의사소통, 영미 문학 읽기, 세계 문화와 영어</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>약사</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>화학, 생명과학, 물질과 에너지, 화학 반응의 세계, 세포와 물질대사, 생물의 유전</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>역사학자/학예사/큐레이터</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>영미 문학 읽기, 세계사, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 한문 과목 전반</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>에너지/환경 기술자</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>대수, 기후변화와 지속가능한 세계, 생태와 환경, 기후변화와 환경생태</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>연극 배우/연출가/기획자</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>문학과 영상, 삶과 종교</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>작곡가/음향전문가</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>대수, 수학과 문화, 음악, 음악 감상과 비평, 음악과 미디어</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>작가(소설가/시인/에세이스트)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어, 독서와 작문, 문학, 문학과 영상, 독서 토론과 글쓰기, 영어Ⅱ, 영미 문학 읽기, 미디어 영어, 세계사, 현대사회와 윤리, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 기후변화와 지속가능한 세계, 인간과 철학, 제2외국어 및 한문 과목 전반</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>전기전자공학자</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>대수, 미적분 I, 미적분 II, 기하, 전자기와 양자, 융합과학 탐구</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>정치인/정치학연구원</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어, 정치</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>철학/인문학 연구원</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>주제 탐구 독서, 언어생활 탐구, 세계사, 현대사회와 윤리, 윤리와 사상, 인문학과 윤리, 인간과 철학, 논리와 사고</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>천문/기상학자</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>대수, 확률과 통계, 융합과학 탐구, 지구과학, 행성우주과학</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>체육/스포츠 전문가(코치/트레이너 등)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>체육1, 체육2, 운동과 건강, 스포츠 문화, 스포츠 과학, 스포츠 생활1, 스포츠 생활2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>통계학자/통계청 공무원</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>대수, 미적분 I, 확률과 통계, 미적분 II, 직무 수학, 수학과 문화, 실용 통계</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>항공우주공학자</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>대수, 기하, 물리학, 역학과 에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>화학공학자/신소재 연구원</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>대수, 미적분 I, 미적분 II, 화학, 물질과 에너지, 화학 반응의 세계, 융합과학 탐구</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sheet/통합시트_예시.xlsx
+++ b/sheet/통합시트_예시.xlsx
@@ -16,20 +16,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="거점형 선택 교육과정" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="과목소개" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="직업데이터" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_선택군" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_규칙" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_과목데이터" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_편제표" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_선택군" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_규칙" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_과목데이터" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_편제표" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_선택군" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_규칙" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_과목데이터" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_편제표" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_규칙작성법" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_2026_조건(참고)" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="용어풀이" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_선택군" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_규칙" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_과목데이터" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2027_편제표" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_선택군" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_규칙" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_과목데이터" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026_편제표" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_선택군" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_규칙" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_과목데이터" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025_편제표" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_규칙작성법" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_2026_조건(참고)" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -121,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -149,6 +150,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -548,304 +555,327 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>🟧 기본정보</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>기본정보</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>입학년도별 열(2025·2026·2027). 학생공개 O인 학년만 학생 화면의 입학년도 목록에 보임</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>입학년도별 열(2025·2026·2027). 학생공개 O인 학년만 학생 화면의 입학년도 목록에 보임
+공지 줄: 화면 맨 위 알림 띠 (날짜를 앞에 쓰면 D-day 표시)</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>새 입학년도 열 추가, 졸업 학년 열 삭제</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>🟩 공통</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>계열데이터</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>계열별 권장 선택과목·전공 선택 팁·관련 학과 (모든 학년 공통)
 출처: 2026 계열별 학과 안내(7개 분야, 19개 계열)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>필요할 때만 수정</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>🟩 공통</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>학과데이터</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>학과 설명·추천 학생·권장 선택과목·개설 대학(서울/수도권/비수도권)·전공 교과목·유사학과·졸업 후 진로
 출처: 2026 계열별 학과 안내</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>필요할 때만 수정</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>🟩 공통</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>대학별 이수권장과목</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>대학·모집단위별 권장 과목</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>대학 발표 시 수정</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>🟩 공통</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>과목소개</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>과목 한줄소개·키워드·배우는 내용·심화 활동·추천 학생·영상 (과목명으로 학년별 과목데이터와 연결)
 출처: 2026학년도 고등학교 선택 과목 안내서(서울시교육청). 참고_ 열은 안내서 값이며 실제 편성·평가는 학년별 과목데이터를 따름</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>새 과목이 생기면 줄 추가</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>🟩 공통</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>직업데이터</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>직업별 관련 과목 (현재 웹페이지에서는 사용하지 않음)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>직업별 관련 과목 → 화면 [① 진로 찾기 → 직업으로 찾기]에서 사용</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>필요할 때만 수정</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>🟩 공통</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>용어풀이</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>화면의 ⓘ 버튼과 [도움말]에 나오는 용어 설명. 줄을 추가하거나 설명을 고치면 바로 반영</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>필요할 때만 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>🟩 공통</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>공유캠퍼스</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>운영 학교와 학기별 과목 (과목 카드에 학교명 표시)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>매 학년도 초 확인</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>🟩 공통</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>거점형 선택 교육과정</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>거점학교 개설 과목 안내 (보관용)</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>매 학년도 초 확인</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>🟦 학년별</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>2027_선택군</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>선택군(A~K): 학기, 몇 과목 선택, 학점, 공유캠퍼스 여부</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>새 입학년도: 작년 탭 복사 후 수정</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>🟦 학년별</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>2027_규칙</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>수강신청 조건 (예전 [조건] 탭을 대신함). 작성법은 _규칙작성법 탭</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>새 입학년도: 작년 탭 복사 후 수정</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>🟦 학년별</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>2027_과목데이터</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>학년마다 다른 것만: 과목명, 편성(예: 2학년 2A군(2학년 1학기) 선택), 학점, 교과군, 선택유형, 평가, 수능출제</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>새 입학년도: 작년 탭 복사 후 수정</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>🟦 학년별</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>2027_편제표</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>학점 배당표 (편제표 화면에 그대로 표시)</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>새 입학년도: 확정 편제표 붙여 넣기</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>⬜ 전송 안 함</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>_로 시작하는 탭</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>웹페이지로 보내지 않음: 사용안내, 메모, 참고 자료, 학생 명단 등</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
-      <c r="B15" s="2" t="inlineStr"/>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
+      <c r="D15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>새 입학년도 추가 순서</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>① 작년 학년별 탭 4개를 복사 → 이름 앞 연도를 새 연도로 변경 (예: 2028_과목데이터)
 ② 기본정보에 새 연도 열 추가 (학생공개는 X로 시작)
@@ -854,31 +884,31 @@
 ⑤ 졸업한 학년의 탭 4개와 기본정보 열 삭제</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="D17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>탭 이름 규칙</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>학년별 탭은 반드시 "4자리 연도_탭이름" 형식. 연도 뒤 이름(선택군, 규칙, 과목데이터, 편제표)은 바꾸지 마세요.
 공통 탭과 같은 이름의 학년별 탭이 있으면(예: 2027_공유캠퍼스) 그 학년은 학년별 탭을 사용합니다.</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="D18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>예시 파일 안내</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr"/>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>2026: 기존 시트 자료 (공유캠퍼스 2과목의 편성 오류 수정함)
 2027: 2026 자료를 복사해 둔 것 → 2027 편제가 확정되면 수정. 과학중점 규칙은 뺐고 운영과정은 "일반"
@@ -886,7 +916,7 @@
 과목소개: 기존 과목데이터의 소개 열 + 기존 과목소개 탭을 과목명으로 합침</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr"/>
+      <c r="D19" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -894,6 +924,253 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0016A34A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>용어</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>고교학점제</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>학생이 진로와 적성에 따라 과목을 골라 듣고, 기준에 도달한 과목의 학점을 쌓아 졸업하는 제도입니다. 3년간 192학점 이상을 취득해야 졸업합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>학점</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>과목의 수업 양입니다. 1학점은 한 학기 동안 일주일에 1시간(50분) 수업을 뜻합니다. 예) 4학점 = 주 4시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>공통 과목</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>모든 학생이 1학년 때 배우는 기초 과목입니다. 예) 공통국어1, 공통수학1, 통합사회1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>일반 선택</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>각 교과의 기본이 되는 선택 과목입니다. 예) 문학, 대수, 물리학. 대부분 수능 출제 범위와 관련이 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>진로 선택</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>일반 선택보다 깊이 있게 배우거나 진로와 관련된 내용을 다루는 과목입니다. 예) 기하, 역학과 에너지</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>융합 선택</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>여러 교과의 내용을 묶거나 실생활에 적용하는 과목입니다. 예) 실용 통계, 기후변화와 환경생태</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>성취도</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>절대평가 결과입니다. 정해진 기준에 얼마나 도달했는지로 A~E(일부 과목 A~C, P)를 받습니다. 다른 학생과 비교하지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>석차등급</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>상대평가 결과입니다. 같은 과목을 듣는 학생 안에서의 순위에 따라 1~5등급을 받습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>절대 평가</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>정해진 성취 기준에 따라 성취도(A~E 등)를 매기는 평가입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>상대 평가</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>같은 과목 수강생 안에서의 순위로 석차등급(1~5등급)을 매기는 평가입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>수능 출제</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>대학수학능력시험(수능) 출제 범위에 들어가는 과목입니다. 표시된 수능 연도를 확인하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>선택군</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>같은 학기에 함께 열리는 과목 묶음입니다. "택3"은 그 묶음에서 3과목을 골라야 한다는 뜻입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>학교 지정 과목</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>학교가 모든 학생에게 정해 둔 과목입니다. 따로 고르지 않아도 편제표에 들어갑니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>공유캠퍼스</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>가까운 여러 학교가 함께 여는 과목입니다. 다른 학교에서 (주로 금요일 오후나 주말에) 수업을 듣고, 희망자만 신청합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>거점형 선택 교육과정</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>특정 학교(거점학교)가 개설한 과목을 다른 학교 학생도 신청해 듣는 제도입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>일반 과정</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>대부분의 학생이 따르는 과정으로, 정해진 조건 안에서 과목을 자유롭게 고릅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>과학중점 과정</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>수학·과학·정보 과목을 많이 이수하는 과정입니다. 지정된 과목과 이수 학점 조건을 지켜야 합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>이수 기준</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>과목을 이수(통과)하려면 출석률 2/3 이상이 필요하며, 공통 과목은 학업성취율 40% 이상도 필요합니다. 미달하면 보충 지도를 받습니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001D4ED8"/>
@@ -1296,7 +1573,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001D4ED8"/>
@@ -1783,7 +2060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001D4ED8"/>
@@ -6834,7 +7111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001D4ED8"/>
@@ -11086,7 +11363,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003B82F6"/>
@@ -11489,7 +11766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003B82F6"/>
@@ -12314,7 +12591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003B82F6"/>
@@ -17365,7 +17642,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003B82F6"/>
@@ -21617,7 +21894,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0093C5FD"/>
@@ -21684,7 +21961,265 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>학생공개</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>O = 학생 입학년도 목록에 보임 / X = 숨김 (주소에 ?year=2027 을 붙이면 선생님은 미리보기 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>운영과정</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>일반, 과학중점</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>일반, 과학중점</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>"일반"만 적으면 과학중점 과정 선택이 화면에서 사라지고 일반 과정으로 고정됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>학교명</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>휘경여자고등학교</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>휘경여자고등학교</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>휘경여자고등학교</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>보고서 제목 등에 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>학교약칭</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>휘경여고</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>휘경여고</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>휘경여고</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"휘경여고 편제표" 등에 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>수능년도</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>"29수능 출제" 표시에 사용 (입학년도 + 3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>학기별교과학점</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>편제표에서 학기 합계가 이 학점 이상이면 파란색</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>자료출처</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2025학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2027학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>화면 상단 자료출처 문구</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr"/>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>한 줄에 하나씩. "2027-03-05 수강신청 마감"처럼 날짜를 앞에 쓰면 D-day가 붙고, 날짜가 지나면 자동으로 숨겨짐. 날짜 없이 쓰면 항상 보임. 비워 두면 알림 띠가 나타나지 않음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:Z2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"O,X"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0093C5FD"/>
@@ -21789,250 +22324,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>설명</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>학생공개</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>O = 학생 입학년도 목록에 보임 / X = 숨김 (주소에 ?year=2027 을 붙이면 선생님은 미리보기 가능)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>운영과정</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>일반, 과학중점</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>일반, 과학중점</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>"일반"만 적으면 과학중점 과정 선택이 화면에서 사라지고 일반 과정으로 고정됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>학교명</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>휘경여자고등학교</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>휘경여자고등학교</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>휘경여자고등학교</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>보고서 제목 등에 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>학교약칭</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>휘경여고</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>휘경여고</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>휘경여고</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>"휘경여고 편제표" 등에 표시</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>수능년도</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>"29수능 출제" 표시에 사용 (입학년도 + 3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>학기별교과학점</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>편제표에서 학기 합계가 이 학점 이상이면 파란색</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>자료출처</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>2025학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2026학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2027학년도 2022 개정 교육과정 선택 과목 안내서(서울특별시교육청)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>화면 상단 자료출처 문구</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:Z2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"O,X"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0093C5FD"/>
@@ -22099,7 +22391,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0093C5FD"/>
@@ -22124,7 +22416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>
@@ -22384,7 +22676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>

--- a/sheet/통합시트_예시.xlsx
+++ b/sheet/통합시트_예시.xlsx
@@ -681,7 +681,8 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>직업별 관련 과목 → 화면 [① 진로 찾기 → 직업으로 찾기]에서 사용</t>
+          <t>직업별 관련 과목·하는 일·과목별 추천 이유("과목명: 이유" 한 줄씩) → 화면 [① 진로 찾기 → 직업으로 찾기]
+※ 하는 일·추천 이유는 초안이므로 선생님 검토 후 사용</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -70199,22 +70200,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>직업</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>휘경여고 개설 필요(관련) 과목</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>하는 일</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>과목별 추천 이유</t>
         </is>
       </c>
     </row>
@@ -70229,6 +70242,18 @@
           <t>음악, 음악 감상과 비평, 음악과 미디어</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>노래나 악기로 음악을 표현하고 무대에서 공연하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>음악: 정확한 음정·리듬과 표현력이 기본이라 → 노래·연주·창작의 기초를 다져요.
+음악 감상과 비평: 곡을 깊이 해석해야 개성 있는 연주가 나와서 → 여러 시대·장르의 음악을 분석하고 비평해요.
+음악과 미디어: 요즘 음악은 녹음·영상·온라인으로 소비되므로 → 미디어를 활용한 음악 제작과 홍보를 경험해요.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -70241,6 +70266,21 @@
           <t>화학, 생명과학, 물질과 에너지, 화학 반응의 세계, 세포와 물질대사, 생물의 유전</t>
         </is>
       </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>환자를 돌보고 투약·처치를 하며, 학교·지역의 건강을 관리하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>화학: 약물의 성분과 투약 용량을 다루므로 → 물질의 성질과 화학 반응의 기초를 배워요.
+생명과학: 사람 몸의 구조와 질병을 이해해야 하므로 → 세포·항상성·면역 등 생명 현상의 기초를 배워요.
+물질과 에너지: 수액·약물의 농도와 체내 물질 변화를 이해해야 해서 → 물질의 상태와 용액의 성질을 깊이 배워요.
+화학 반응의 세계: 약이 몸에서 어떻게 작용하는지 알아야 해서 → 산·염기, 산화·환원 같은 반응을 깊이 배워요.
+세포와 물질대사: 환자의 대사·영양 상태를 판단해야 해서 → 세포 호흡과 물질대사의 원리를 배워요.
+생물의 유전: 유전 질환 상담과 건강 교육에 필요해서 → 유전의 원리와 유전자 기술을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -70253,6 +70293,24 @@
           <t>경제 수학, 세계사, 한국지리 탐구, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 법과 사회, 경제, 금융과 경제생활, 인간과 경제활동</t>
         </is>
       </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>토지·건물·기업 자산의 경제적 가치를 평가해 가격을 매기는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>경제 수학: 가격·수익률·감가상각을 계산하므로 → 경제 현상을 수학으로 분석하는 법을 배워요.
+세계사: 자산 가치는 역사·국제 흐름의 영향을 받아서 → 세계의 변화와 그 배경을 이해해요.
+한국지리 탐구: 땅값은 위치·지형·교통에 따라 달라져서 → 우리나라 지역의 특성을 탐구해요.
+동아시아 역사 기행: 주변국과의 관계가 경제·부동산에 영향을 주므로 → 동아시아 역사와 교류를 이해해요.
+역사로 탐구하는 현대 세계: 경제 위기·정책 변화가 자산 가치를 바꾸므로 → 현대 세계의 흐름을 탐구해요.
+법과 사회: 감정평가는 법에 따라 이루어지므로 → 재산권·계약 등 생활 속 법을 배워요.
+경제: 시장 가격이 어떻게 정해지는지 알아야 해서 → 수요·공급과 시장의 원리를 배워요.
+금융과 경제생활: 대출·투자·세금이 자산 가치와 연결되어서 → 금융 상품과 경제생활을 배워요.
+인간과 경제활동: 사람들의 경제적 선택을 이해해야 해서 → 경제활동과 합리적 의사결정을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -70265,6 +70323,19 @@
           <t>대수, 기하, 직무 수학, 도시의 미래 탐구</t>
         </is>
       </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>건물을 설계하고 구조가 안전한지 계산하며 시공을 관리하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>대수: 하중·비용·면적을 정확히 계산해야 해서 → 수식과 함수 계산 능력을 길러요.
+기하: 도면을 그리고 공간을 입체로 생각해야 해서 → 도형·벡터·공간 좌표를 배워요.
+직무 수학: 현장에서 측량·견적·비율 계산을 하므로 → 실무에 쓰이는 수학을 배워요.
+도시의 미래 탐구: 건물은 도시 환경 속에 지어지므로 → 도시 구조와 지속가능한 도시 계획을 탐구해요.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -70277,6 +70348,22 @@
           <t>화법과 언어, 독서와 작문, 직무 의사소통, 독서 토론과 글쓰기, 언어생활 탐구, 정치, 법과 사회</t>
         </is>
       </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>법을 해석하고 증거를 따져 사건을 판단하거나, 의뢰인을 대신해 변론하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어: 법정에서 논리적으로 말하고 설득해야 해서 → 설득 전략과 정확한 언어 사용을 배워요.
+독서와 작문: 판결문·소장 등 긴 글을 읽고 써야 해서 → 비판적 읽기와 논증적 글쓰기를 배워요.
+직무 의사소통: 의뢰인 상담과 협상이 일의 중심이라 → 직업 상황의 말하기·쓰기를 배워요.
+독서 토론과 글쓰기: 쟁점을 따지고 반론을 세워야 해서 → 토론과 논리적 글쓰기를 연습해요.
+언어생활 탐구: 법조문의 단어 하나가 판결을 바꾸므로 → 언어의 의미와 쓰임을 정확히 탐구해요.
+정치: 법은 국가 제도와 권력 구조 속에서 작동하므로 → 민주주의와 정치 제도를 배워요.
+법과 사회: 모든 업무의 기초가 법이라 → 헌법·민법·형법 등 법의 원리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -70289,6 +70376,20 @@
           <t>수학과 문화, 문학과 영상, 정보, 인공지능 기초, 인간과 심리</t>
         </is>
       </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>게임의 세계관과 이야기를 만들고, 규칙을 설계하며 프로그램으로 구현하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>수학과 문화: 게임 규칙·확률·밸런스에 수학이 쓰이므로 → 생활과 문화 속 수학을 탐구해요.
+문학과 영상: 몰입감 있는 스토리가 게임의 힘이라 → 서사 구조와 영상 표현을 배워요.
+정보: 게임은 결국 프로그램이라 → 알고리즘과 프로그래밍의 기초를 배워요.
+인공지능 기초: NPC 행동·추천 시스템에 AI가 쓰이므로 → 인공지능의 원리와 활용을 배워요.
+인간과 심리: 플레이어가 재미를 느끼는 이유를 알아야 해서 → 사람의 동기와 심리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -70301,6 +70402,28 @@
           <t>화법과 언어, 독서와 작문, 직무 의사소통, 독서 토론과 글쓰기, 매체 의사소통, 언어생활 탐구, 직무 수학, 현대사회와 윤리, 경제, 윤리와 사상, 인문학과 윤리, 윤리문제 탐구, 인간과 경제활동</t>
         </is>
       </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>기업의 전략을 세우고 상품·서비스를 알리며 고객과 소통하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어: 발표·협상·고객 응대가 많아서 → 상황에 맞는 설득적 말하기를 배워요.
+독서와 작문: 보고서·기획서를 많이 써서 → 자료를 읽고 논리적으로 쓰는 힘을 길러요.
+직무 의사소통: 회의·이메일·프레젠테이션이 일상이라 → 직장 상황의 의사소통을 배워요.
+독서 토론과 글쓰기: 팀에서 아이디어를 주고받으며 결정하므로 → 토론과 설득하는 글쓰기를 연습해요.
+매체 의사소통: 광고·SNS로 소비자와 만나므로 → 매체별 메시지 전략을 배워요.
+언어생활 탐구: 광고 문구 한 줄이 반응을 바꾸므로 → 언어의 효과와 쓰임을 탐구해요.
+직무 수학: 매출·예산·시장 자료를 분석해야 해서 → 실무에 쓰이는 수학과 자료 해석을 배워요.
+현대사회와 윤리: 기업의 사회적 책임이 중요해져서 → 현대 사회의 윤리 문제를 생각해요.
+경제: 시장과 소비자의 움직임을 읽어야 해서 → 수요·공급과 경제 원리를 배워요.
+윤리와 사상: 경영 철학과 가치 판단의 바탕이 되므로 → 동서양 윤리 사상을 배워요.
+인문학과 윤리: 사람을 이해하는 경영이 필요해서 → 인문학적 성찰과 윤리를 배워요.
+윤리문제 탐구: 광고 윤리·개인정보 같은 쟁점을 다루므로 → 실제 윤리 문제를 탐구해요.
+인간과 경제활동: 소비자 행동을 이해해야 해서 → 사람의 경제적 선택과 활동을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -70313,6 +70436,26 @@
           <t>직무 의사소통, 직무 수학, 수학과 문화, 세계사, 도시의 미래 탐구, 한국지리 탐구, 정치, 사회문제 탐구, 기후변화와 지속가능한 세계, 법과 사회, 인간과 경제활동</t>
         </is>
       </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>국가·지방자치단체에서 정책을 만들고 시행하며 국민에게 행정 서비스를 제공하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>직무 의사소통: 민원 응대와 공문서 작성이 많아서 → 직업 상황의 말하기·쓰기를 배워요.
+직무 수학: 예산·통계 자료를 다루므로 → 실무에 쓰이는 계산과 자료 해석을 배워요.
+수학과 문화: 정책 판단에 수학적 사고가 쓰여서 → 생활 속 수학의 쓰임을 탐구해요.
+세계사: 정책은 세계 흐름과 연결되므로 → 세계의 역사와 변화를 이해해요.
+도시의 미래 탐구: 교통·주거 등 도시 정책을 다루므로 → 도시 문제와 미래 도시를 탐구해요.
+한국지리 탐구: 지역마다 필요한 정책이 달라서 → 우리나라 지역의 특성을 탐구해요.
+정치: 정책은 정치 과정을 거쳐 만들어지므로 → 민주주의와 정부의 역할을 배워요.
+사회문제 탐구: 저출생·불평등 같은 문제를 해결해야 해서 → 사회 문제의 원인과 대책을 탐구해요.
+기후변화와 지속가능한 세계: 기후·환경 정책이 중요해져서 → 지속가능한 발전 방안을 탐구해요.
+법과 사회: 모든 행정은 법에 따라 이루어지므로 → 법의 원리와 생활 속 법을 배워요.
+인간과 경제활동: 경제 정책의 영향을 이해해야 해서 → 경제활동의 원리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -70325,6 +70468,20 @@
           <t>영어 독해와 작문, 영어II, 실생활 영어 회화, 미디어 영어, 제2외국어 과목 전반 (일본어, 중국어, 일본어 회화, 중국어 회화, 일본 문화, 중국 문화 등)</t>
         </is>
       </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>외국인 관광객에게 우리나라의 문화와 명소를 외국어로 안내하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>영어 독해와 작문: 안내 자료를 읽고 만들어야 해서 → 정확한 영어 읽기·쓰기를 배워요.
+영어II: 관광객과 막힘없이 소통해야 해서 → 영어 의사소통 능력을 넓혀요.
+실생활 영어 회화: 현장에서 바로 말하는 일이라 → 생활 속 영어 회화를 연습해요.
+미디어 영어: 여행 정보·후기를 영어 매체로 접하므로 → 영어 미디어를 이해하고 활용해요.
+제2외국어: 일본·중국 관광객이 많아서 → 해당 언어와 문화를 배우면 안내 폭이 넓어져요.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -70337,6 +70494,17 @@
           <t>주제 탐구 독서, 교육의 이해</t>
         </is>
       </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>학생이 잘 배우는 방법을 연구하고 교육 정책·교육과정 개발에 참여하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>주제 탐구 독서: 연구는 자료를 깊이 읽는 데서 시작해서 → 한 주제를 정해 깊이 읽고 탐구해요.
+교육의 이해: 교육의 목적과 방법이 연구의 중심이라 → 교육학의 기초를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -70349,6 +70517,21 @@
           <t>화법과 언어, 독서와 작문, 문학, 주제 탐구 독서, 독서 토론과 글쓰기, 언어생활 탐구</t>
         </is>
       </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>우리말과 문학을 가르치거나, 언어의 구조와 변화를 연구하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어: 수업은 말하기로 이루어지고 문법은 핵심 내용이라 → 화법과 국어 문법을 배워요.
+독서와 작문: 읽기·쓰기 지도가 국어 수업의 중심이라 → 읽기 전략과 글쓰기를 배워요.
+문학: 작품을 해석하고 가르쳐야 해서 → 시·소설·수필 등 문학 감상을 깊이 배워요.
+주제 탐구 독서: 연구와 수업 준비에 깊이 있는 읽기가 필요해서 → 주제 중심 독서를 해요.
+독서 토론과 글쓰기: 토론 수업을 이끌어야 해서 → 토론과 논증적 글쓰기를 경험해요.
+언어생활 탐구: 실제 언어 사용을 연구하므로 → 생활 속 언어 현상을 탐구해요.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -70361,6 +70544,23 @@
           <t>영어Ⅰ, 영어 발표와 토론, 심화 영어, 세계사, 세계시민과 지리, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 정치</t>
         </is>
       </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>다른 나라와 협상하고 국가의 이익을 지키며 국제 협력을 이끄는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>영어Ⅰ: 외교의 공용어가 영어라서 → 영어 의사소통의 기초를 탄탄히 해요.
+영어 발표와 토론: 국제회의에서 발표하고 협상해야 해서 → 영어로 발표·토론하는 법을 익혀요.
+심화 영어: 외교 문서와 고급 표현을 다루므로 → 수준 높은 영어를 배워요.
+세계사: 나라 사이의 관계는 역사에서 비롯되므로 → 세계사의 흐름을 이해해요.
+세계시민과 지리: 국제 문제는 지역 특성과 연결돼서 → 세계 지리와 세계시민 의식을 배워요.
+동아시아 역사 기행: 주변국 외교가 특히 중요해서 → 동아시아의 역사와 갈등·협력을 탐구해요.
+역사로 탐구하는 현대 세계: 오늘의 국제 질서를 이해해야 해서 → 현대 세계의 형성 과정을 배워요.
+정치: 외교는 국제 정치의 한 부분이라 → 정치 제도와 국제 관계를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -70373,6 +70573,22 @@
           <t>대수, 미적분 I, 미적분 II, 기하, 물리학, 역학과 에너지, 융합과학 탐구</t>
         </is>
       </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>기계와 로봇을 설계·제작하고 움직임을 제어하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>대수: 설계 계산의 기본이 되므로 → 수식·함수 계산 능력을 길러요.
+미적분 I: 속도·가속도처럼 변화를 다뤄야 해서 → 미분·적분의 기초를 배워요.
+미적분 II: 복잡한 운동과 제어를 계산해야 해서 → 심화 미적분을 배워요.
+기하: 부품의 모양과 로봇 팔의 위치를 계산해야 해서 → 벡터와 공간도형을 배워요.
+물리학: 기계는 힘과 운동의 법칙으로 움직이므로 → 역학·전기의 기초를 배워요.
+역학과 에너지: 움직임과 에너지 효율이 설계의 핵심이라 → 힘과 운동, 에너지를 깊이 배워요.
+융합과학 탐구: 로봇은 여러 과학이 합쳐진 기술이라 → 융합적으로 탐구하는 경험을 해요.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -70385,6 +70601,38 @@
           <t>화법과 언어, 독서와 작문, 문학, 주제 탐구 독서, 독서 토론과 글쓰기, 매체 의사소통, 언어생활 탐구, 영미 문학 읽기, 직무 영어, 세계 문화와 영어, 세계사, 세계시민과 지리, 도시의 미래 탐구, 한국지리 탐구, 정치, 사회문제 탐구, 기후변화와 지속가능한 세계, 인간과 철학, 논리와 사고, 인간과 심리, 삶과 종교, 제2외국어 및 한문 과목 전반</t>
         </is>
       </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>사회의 사건과 이슈를 취재해 정확한 기사와 방송으로 전달하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어: 인터뷰와 보도에서 정확히 말해야 해서 → 말하기 전략과 바른 언어를 배워요.
+독서와 작문: 자료를 빠르게 읽고 기사를 써야 해서 → 비판적 읽기와 글쓰기를 배워요.
+문학: 사람의 이야기를 생생하게 전하는 힘이 필요해서 → 문학적 표현과 해석을 배워요.
+주제 탐구 독서: 심층 취재는 깊은 자료 조사에서 시작돼서 → 한 주제를 깊이 읽어요.
+독서 토론과 글쓰기: 쟁점을 균형 있게 다뤄야 해서 → 토론과 논증적 글쓰기를 연습해요.
+매체 의사소통: 신문·방송·SNS로 소식을 전하므로 → 매체별 표현과 미디어 윤리를 배워요.
+언어생활 탐구: 단어 선택이 기사의 공정성을 좌우해서 → 언어의 쓰임을 탐구해요.
+영미 문학 읽기: 해외 문화와 시각을 이해해야 해서 → 영어권 문학을 읽어요.
+직무 영어: 해외 취재·외신 자료를 다루므로 → 실무 영어를 배워요.
+세계 문화와 영어: 국제 뉴스를 다루려면 문화 이해가 필요해서 → 세계 문화를 영어로 배워요.
+세계사: 국제 뉴스의 배경을 설명해야 해서 → 세계사의 흐름을 이해해요.
+세계시민과 지리: 세계 곳곳의 문제를 보도하므로 → 세계 지리와 지구촌 문제를 배워요.
+도시의 미래 탐구: 도시·주거 문제를 자주 다뤄서 → 도시 문제를 탐구해요.
+한국지리 탐구: 지역 소식을 취재하므로 → 우리나라 지역의 특성을 이해해요.
+정치: 정치 뉴스가 보도의 중심이라 → 정치 제도와 과정을 배워요.
+사회문제 탐구: 사회 문제를 깊이 있게 보도해야 해서 → 문제의 원인과 해결책을 탐구해요.
+기후변화와 지속가능한 세계: 기후·환경 보도가 늘어나서 → 지속가능성 문제를 탐구해요.
+인간과 철학: 무엇이 옳은 보도인지 판단해야 해서 → 철학적 사고를 길러요.
+논리와 사고: 주장의 허점과 가짜 뉴스를 가려내야 해서 → 논리적·비판적 사고를 배워요.
+인간과 심리: 취재원과 독자를 이해해야 해서 → 사람의 마음과 행동을 배워요.
+삶과 종교: 다양한 가치관을 존중해 보도해야 해서 → 여러 종교와 문화를 이해해요.
+제2외국어: 해외 취재와 외신 이해에 도움이 돼서 → 외국어와 그 나라 문화를 배워요.
+한문: 한자어가 많은 기사 문장을 정확히 쓰기 위해 → 한문과 한자 어휘를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -70397,6 +70645,17 @@
           <t>직무 의사소통, 법과 사회</t>
         </is>
       </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>노동자와 회사 사이의 노동 문제를 상담하고 법에 따라 해결하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>직무 의사소통: 노사 양쪽을 상담하고 조정해야 해서 → 직업 상황의 의사소통을 배워요.
+법과 사회: 근로기준법 등 노동법이 업무의 기초라 → 생활 속 법과 권리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -70409,6 +70668,17 @@
           <t>독서 토론과 글쓰기, 논리와 사고</t>
         </is>
       </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>학생들이 생각을 논리적으로 정리해 글로 쓰도록 지도하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>독서 토론과 글쓰기: 읽고 토론하고 쓰는 과정 자체를 가르쳐야 해서 → 토론과 논증적 글쓰기를 경험해요.
+논리와 사고: 논리적 오류를 찾아 고쳐 주어야 해서 → 논증의 구조와 비판적 사고를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -70421,6 +70691,20 @@
           <t>확률과 통계, 인공지능 수학, 직무 수학, 융합과학 탐구, 정보</t>
         </is>
       </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>많은 데이터를 모아 분석하고 숨은 규칙을 찾아 의사결정을 돕는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>확률과 통계: 데이터 분석의 언어가 통계라서 → 확률·분포·추정을 배워요.
+인공지능 수학: 머신러닝은 수학으로 작동하므로 → 인공지능에 쓰이는 수학을 배워요.
+직무 수학: 실제 업무 데이터를 다루므로 → 실무에 쓰이는 수학과 자료 해석을 배워요.
+융합과학 탐구: 과학 데이터를 분석하는 일도 많아서 → 탐구 설계와 자료 분석을 경험해요.
+정보: 데이터는 프로그램으로 처리하므로 → 프로그래밍과 자료 처리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -70433,6 +70717,19 @@
           <t>수학과 문화, 도시의 미래 탐구, 한국지리 탐구, 생태와 환경</t>
         </is>
       </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>사람들이 살기 좋은 도시를 위해 교통·주거·환경을 계획하고 연구하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>수학과 문화: 인구·교통량을 분석하는 데 수학이 쓰여서 → 생활 속 수학의 쓰임을 탐구해요.
+도시의 미래 탐구: 도시 계획의 핵심 주제라 → 도시 구조와 미래 도시를 탐구해요.
+한국지리 탐구: 지역 특성에 맞는 계획을 세워야 해서 → 우리나라 지역을 탐구해요.
+생태와 환경: 친환경 도시가 중요해져서 → 생태계와 환경 문제를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -70445,6 +70742,25 @@
           <t>영어Ⅰ, 영어 독해와 작문, 영어II, 직무 영어, 미디어 영어, 세계 문화와 영어, 세계시민과 지리, 경제, 인간과 경제활동, 제2외국어 과목 전반</t>
         </is>
       </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>다른 나라와 상품·서비스를 사고팔며 계약·통관·물류를 처리하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>영어Ⅰ: 해외 거래처와 영어로 소통해야 해서 → 영어 의사소통의 기초를 다져요.
+영어 독해와 작문: 계약서·이메일을 영어로 읽고 써야 해서 → 정확한 영어 읽기·쓰기를 배워요.
+영어II: 협상과 설명을 영어로 해야 해서 → 영어 의사소통 능력을 넓혀요.
+직무 영어: 무역 서류와 업무 영어를 다뤄서 → 실무 영어를 배워요.
+미디어 영어: 해외 시장 정보를 영어 매체로 얻어서 → 영어 미디어 활용법을 익혀요.
+세계 문화와 영어: 나라마다 거래 문화가 달라서 → 세계 문화를 영어로 이해해요.
+세계시민과 지리: 어느 나라에서 무엇을 사고팔지 알아야 해서 → 세계 지리와 자원을 배워요.
+경제: 환율·관세·무역 원리를 알아야 해서 → 국제 경제의 기초를 배워요.
+인간과 경제활동: 소비자와 기업의 선택을 이해해야 해서 → 경제활동의 원리를 배워요.
+제2외국어: 중국·일본 등과의 교역이 많아서 → 해당 언어와 문화를 배우면 큰 도움이 돼요.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -70457,6 +70773,19 @@
           <t>독서와 작문, 문학, 주제 탐구 독서, 언어생활 탐구</t>
         </is>
       </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>책과 정보를 수집·정리하고 이용자가 필요한 자료를 찾도록 돕는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>독서와 작문: 자료를 읽고 소개 글을 써야 해서 → 읽기 전략과 글쓰기를 배워요.
+문학: 좋은 책을 골라 추천해야 해서 → 문학 작품을 폭넓게 감상해요.
+주제 탐구 독서: 주제별로 자료를 찾아 주는 일이 많아서 → 주제 중심 독서를 경험해요.
+언어생활 탐구: 정보를 분류하고 검색어를 다루므로 → 언어와 정보의 관계를 탐구해요.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -70469,6 +70798,18 @@
           <t>운동과 건강, 생명과학, 세포와 물질대사</t>
         </is>
       </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>다친 몸의 움직임을 회복하도록 운동·치료 프로그램을 세워 돕는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>운동과 건강: 운동으로 몸을 회복시키는 일이라 → 운동의 원리와 건강 관리를 배워요.
+생명과학: 근육·신경·뼈의 작용을 알아야 해서 → 사람 몸의 구조와 기능을 배워요.
+세포와 물질대사: 회복 과정은 세포 수준에서 일어나서 → 세포와 에너지 대사를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -70481,6 +70822,21 @@
           <t>대수, 미적분 I, 미적분 II, 물리학, 역학과 에너지, 전자기와 양자</t>
         </is>
       </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>자연의 근본 법칙을 연구하고 실험과 수학으로 증명하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>대수: 물리 법칙은 수식으로 표현되므로 → 수식과 함수 계산 능력을 길러요.
+미적분 I: 운동과 변화를 설명하는 언어라서 → 미분·적분의 기초를 배워요.
+미적분 II: 복잡한 물리 현상을 계산해야 해서 → 심화 미적분을 배워요.
+물리학: 연구의 출발점이라 → 역학·전자기·빛의 기초를 배워요.
+역학과 에너지: 운동과 에너지는 물리학의 중심이라 → 역학과 열역학을 깊이 배워요.
+전자기와 양자: 반도체·양자 기술 연구의 바탕이라 → 전자기와 양자 물리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -70493,6 +70849,20 @@
           <t>기하, 수학과 문화, 미술, 미술 감상과 비평, 미술과 매체</t>
         </is>
       </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>시각 자료나 제품을 아름답고 쓰기 좋게 디자인하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>기하: 형태·비례·원근을 정확히 다뤄야 해서 → 도형과 공간 감각을 길러요.
+수학과 문화: 황금비·대칭 같은 수학이 디자인에 쓰여서 → 예술 속 수학을 탐구해요.
+미술: 표현과 조형의 기초가 필요해서 → 다양한 재료와 기법으로 표현해요.
+미술 감상과 비평: 좋은 디자인을 보는 눈을 길러야 해서 → 작품을 분석하고 비평해요.
+미술과 매체: 디지털 매체로 작업하는 일이 많아서 → 다양한 매체 표현을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -70505,6 +70875,26 @@
           <t>매체 의사소통, 문학, 문학과 영상, 영미 문학 읽기, 세계 문화와 영어, 세계시민과 지리, 사회와 문화, 역사로 탐구하는 현대 세계, 기후변화와 지속가능한 세계, 사회문제 탐구, 삶과 종교</t>
         </is>
       </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>방송 프로그램을 기획하고 촬영·편집을 지휘해 완성하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>매체 의사소통: 시청자에게 전달되는 방식을 설계해야 해서 → 매체 언어와 표현을 배워요.
+문학: 이야기를 만드는 힘이 필요해서 → 서사와 인물 표현을 배워요.
+문학과 영상: 글을 영상으로 바꾸는 일이라 → 문학과 영상 표현의 관계를 배워요.
+영미 문학 읽기: 해외 콘텐츠와 소재를 폭넓게 접하도록 → 영어권 문학을 읽어요.
+세계 문화와 영어: 해외 촬영·공동 제작이 늘어서 → 세계 문화를 영어로 이해해요.
+세계시민과 지리: 다큐·여행 프로그램의 소재가 되므로 → 세계 지리와 문화를 배워요.
+사회와 문화: 시청자의 관심과 사회 흐름을 읽어야 해서 → 사회·문화 현상을 배워요.
+역사로 탐구하는 현대 세계: 시사·다큐 기획의 배경 지식이 되므로 → 현대 세계의 흐름을 탐구해요.
+기후변화와 지속가능한 세계: 환경 다큐 등 공익 프로그램을 만들 때 → 지속가능성 문제를 탐구해요.
+사회문제 탐구: 시사 프로그램은 사회 문제를 다뤄서 → 문제의 원인과 대책을 탐구해요.
+삶과 종교: 다양한 삶과 가치관을 존중해 담아야 해서 → 여러 종교·문화를 이해해요.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -70517,6 +70907,23 @@
           <t>독서와 작문, 직무 영어, 영어 독해와 작문, 심화 영어 독해와 작문, 심화 영어, 실생활 영어 회화, 세계 문화와 영어, 제2외국어 과목 전반</t>
         </is>
       </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>한 언어의 글과 말을 다른 언어로 정확하고 자연스럽게 옮기는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>독서와 작문: 번역문은 우리말로도 좋은 글이어야 해서 → 정확한 읽기와 글쓰기를 배워요.
+직무 영어: 기업·기관 문서를 많이 번역하므로 → 실무 영어를 배워요.
+영어 독해와 작문: 원문을 정확히 이해해야 해서 → 영어 읽기와 쓰기를 깊이 배워요.
+심화 영어 독해와 작문: 전문 문서를 다루므로 → 수준 높은 영어 독해·작문을 배워요.
+심화 영어: 미묘한 표현 차이를 옮겨야 해서 → 고급 영어를 배워요.
+실생활 영어 회화: 통역은 즉석에서 말해야 해서 → 실제 회화 능력을 키워요.
+세계 문화와 영어: 언어 뒤의 문화를 알아야 바르게 옮겨서 → 세계 문화를 영어로 배워요.
+제2외국어: 영어 외 언어도 다루면 활동 폭이 넓어져서 → 제2외국어와 그 문화를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -70529,6 +70936,17 @@
           <t>법과 사회, 생태와 환경</t>
         </is>
       </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>새 발명과 기술을 특허로 보호받도록 서류를 만들고 분쟁을 대리하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>법과 사회: 특허법 등 지식재산 법을 다루므로 → 법의 원리를 배워요.
+생태와 환경: 친환경 기술 특허가 늘어나서 → 환경과 생태에 대한 이해를 넓혀요.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -70541,6 +70959,19 @@
           <t>확률과 통계, 경제 수학, 법과 사회, 금융과 경제생활</t>
         </is>
       </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>사고·질병이 일어날 확률을 계산해 보험료를 정하거나 손해액을 판단하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>확률과 통계: 보험료는 사고 확률로 계산되므로 → 확률과 통계를 배워요.
+경제 수학: 이자·연금·보험금을 계산해야 해서 → 경제 현상을 수학으로 다뤄요.
+법과 사회: 보험 계약과 손해 배상은 법을 따르므로 → 계약·책임 등 생활 법을 배워요.
+금융과 경제생활: 보험은 금융 상품이라 → 금융 상품과 위험 관리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -70553,6 +70984,17 @@
           <t>교육의 이해, 인간과 심리</t>
         </is>
       </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>영유아를 돌보고 놀이와 활동으로 성장과 배움을 돕는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>교육의 이해: 아이들을 가르치는 방법의 기초라서 → 교육의 의미와 방법을 배워요.
+인간과 심리: 아이의 발달과 마음을 이해해야 해서 → 사람의 발달과 심리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -70565,6 +71007,21 @@
           <t>세계시민과 지리, 사회와 문화, 도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 인간과 심리</t>
         </is>
       </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>사회 현상을 조사·분석해 원인을 밝히고 정책에 필요한 연구를 하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>세계시민과 지리: 사회 현상을 세계와 연결해 봐야 해서 → 세계 지리와 지구촌 문제를 배워요.
+사회와 문화: 사회학의 기초 개념을 다루므로 → 사회 구조와 문화를 배워요.
+도시의 미래 탐구: 도시화가 큰 연구 주제라 → 도시 문제를 탐구해요.
+한국지리 탐구: 지역별 차이를 연구하므로 → 우리나라 지역을 탐구해요.
+사회문제 탐구: 연구 대상이 바로 사회 문제라 → 문제를 조사하고 분석하는 방법을 배워요.
+인간과 심리: 사람들의 행동 이유를 알아야 해서 → 사람의 마음과 행동을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -70577,6 +71034,20 @@
           <t>법과 사회, 도시의 미래 탐구, 한국지리 탐구, 사회문제 탐구, 윤리문제 탐구</t>
         </is>
       </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>도움이 필요한 사람에게 복지 제도를 연결하고 상담하며 삶을 지원하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>법과 사회: 복지 제도는 법으로 정해져 있어서 → 생활 속 법과 권리를 배워요.
+도시의 미래 탐구: 주거·지역 복지 문제를 다루므로 → 도시 문제를 탐구해요.
+한국지리 탐구: 지역마다 필요한 복지가 달라서 → 지역의 특성을 탐구해요.
+사회문제 탐구: 빈곤·고립 같은 문제를 해결해야 해서 → 사회 문제의 원인과 대책을 탐구해요.
+윤리문제 탐구: 어려운 결정을 윤리적으로 내려야 해서 → 실제 윤리 문제를 탐구해요.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -70589,6 +71060,22 @@
           <t>대수, 미적분 I, 미적분 II, 생명과학, 세포와 물질대사, 생물의 유전, 융합과학 탐구</t>
         </is>
       </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>생명 현상을 실험으로 연구하고 의약·농업·환경에 쓰일 기술을 개발하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>대수: 실험 데이터를 수식으로 다루므로 → 계산과 함수의 기초를 길러요.
+미적분 I: 세포 증식 같은 변화를 모델로 나타내므로 → 미분·적분의 기초를 배워요.
+미적분 II: 복잡한 생명 현상 모델을 다루려면 → 심화 미적분을 배워요.
+생명과학: 연구의 기초 지식이라 → 생명 현상의 원리를 배워요.
+세포와 물질대사: 생명 연구의 기본 단위가 세포라서 → 세포와 대사를 깊이 배워요.
+생물의 유전: 유전자 연구가 핵심 분야라 → 유전 원리와 생명공학을 배워요.
+융합과학 탐구: 연구는 여러 과학이 함께 쓰여서 → 탐구 설계와 실험을 경험해요.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -70601,6 +71088,20 @@
           <t>경제 수학, 직무 수학, 경제, 금융과 경제생활, 인간과 경제활동</t>
         </is>
       </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>기업과 개인의 돈의 흐름을 기록·분석하고 세금을 바르게 계산하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>경제 수학: 이자·세금·수익을 계산해야 해서 → 경제 현상을 수학으로 다뤄요.
+직무 수학: 재무 자료를 다루는 일이 많아서 → 실무에 쓰이는 수학을 배워요.
+경제: 기업 활동과 시장을 이해해야 해서 → 경제 원리를 배워요.
+금융과 경제생활: 세금·투자·금융을 상담하므로 → 금융 상품과 경제생활을 배워요.
+인간과 경제활동: 사람과 기업의 경제적 선택을 이해해야 해서 → 경제활동을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -70613,6 +71114,18 @@
           <t>인공지능 수학, 정보, 인공지능 기초</t>
         </is>
       </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>컴퓨터 프로그램과 앱을 설계하고 코드를 작성해 만드는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>인공지능 수학: AI 기능을 만들려면 수학이 필요해서 → 인공지능에 쓰이는 수학을 배워요.
+정보: 개발의 기본이 프로그래밍이라 → 알고리즘과 코딩을 배워요.
+인공지능 기초: AI를 활용한 서비스가 늘어나서 → 인공지능의 원리와 활용을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -70625,6 +71138,18 @@
           <t>생명과학, 세포와 물질대사, 생물의 유전</t>
         </is>
       </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>동물의 질병을 진단·치료하고 가축과 반려동물의 건강을 지키는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>생명과학: 동물의 몸과 질병을 이해해야 해서 → 생명 현상의 기초를 배워요.
+세포와 물질대사: 질병은 세포와 대사의 이상에서 생겨서 → 세포와 대사를 깊이 배워요.
+생물의 유전: 유전 질환과 품종을 다루므로 → 유전 원리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -70637,6 +71162,20 @@
           <t>대수, 미적분 I, 미적분 II, 확률과 통계, 기하</t>
         </is>
       </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>수학의 새로운 정리를 증명하고 여러 분야의 문제를 수학으로 해결하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>대수: 모든 수학의 기본 도구라서 → 수식·함수·수열을 배워요.
+미적분 I: 해석학의 출발점이라 → 극한·미분·적분을 배워요.
+미적분 II: 더 깊은 해석학으로 나아가려면 → 심화 미적분을 배워요.
+확률과 통계: 확률론과 통계학도 주요 분야라 → 확률과 통계를 배워요.
+기하: 공간과 구조를 다루는 분야라 → 벡터와 공간도형을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -70649,6 +71188,16 @@
           <t>인간과 심리</t>
         </is>
       </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>마음의 어려움을 겪는 사람을 상담하고 치료하도록 돕는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>인간과 심리: 상담의 바탕이 사람의 마음을 이해하는 것이라 → 심리학의 기초를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -70661,6 +71210,20 @@
           <t>화법과 언어, 직무 의사소통, 매체 의사소통, 영미 문학 읽기, 세계 문화와 영어</t>
         </is>
       </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>뉴스를 정확히 전하고 프로그램을 자연스럽게 이끄는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어: 정확한 발음과 표준어가 기본이라 → 말하기와 국어 규범을 배워요.
+직무 의사소통: 인터뷰와 진행에서 상황에 맞게 말해야 해서 → 직업 상황의 의사소통을 배워요.
+매체 의사소통: 방송이라는 매체로 전달하므로 → 매체 언어와 표현을 배워요.
+영미 문학 읽기: 폭넓은 교양과 영어 감각이 필요해서 → 영어권 문학을 읽어요.
+세계 문화와 영어: 국제 소식과 해외 게스트를 다루므로 → 세계 문화를 영어로 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -70673,6 +71236,21 @@
           <t>화학, 생명과학, 물질과 에너지, 화학 반응의 세계, 세포와 물질대사, 생물의 유전</t>
         </is>
       </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>약을 조제하고 올바른 복용법을 안내하며 신약 연구에도 참여하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>화학: 약은 화학 물질이라 → 물질의 구조와 반응의 기초를 배워요.
+생명과학: 약이 몸에서 작용하는 원리를 알아야 해서 → 생명 현상의 기초를 배워요.
+물질과 에너지: 약의 용해·농도를 다루므로 → 물질의 상태와 용액을 깊이 배워요.
+화학 반응의 세계: 약효는 화학 반응으로 나타나서 → 산·염기, 산화·환원 반응을 배워요.
+세포와 물질대사: 약이 세포에서 대사되는 과정을 알아야 해서 → 세포와 대사를 배워요.
+생물의 유전: 맞춤 약·유전자 치료가 늘어서 → 유전 원리를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -70685,6 +71263,20 @@
           <t>영미 문학 읽기, 세계사, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 한문 과목 전반</t>
         </is>
       </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>역사 자료를 연구하고 박물관·미술관 전시를 기획해 사람들에게 소개하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>영미 문학 읽기: 해외 자료와 전시를 다루므로 → 영어권 문학과 문화를 읽어요.
+세계사: 연구와 전시의 배경 지식이라 → 세계사의 흐름을 배워요.
+동아시아 역사 기행: 우리 역사는 동아시아와 함께 움직여서 → 동아시아 역사를 탐구해요.
+역사로 탐구하는 현대 세계: 근현대사 자료를 해석해야 해서 → 현대 세계의 형성을 탐구해요.
+한문: 옛 문헌이 한문으로 쓰여 있어서 → 한문을 읽는 힘을 길러요.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -70697,6 +71289,19 @@
           <t>대수, 기후변화와 지속가능한 세계, 생태와 환경, 기후변화와 환경생태</t>
         </is>
       </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>신재생 에너지와 환경 오염을 줄이는 기술을 개발하고 관리하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>대수: 에너지량·오염도를 계산해야 해서 → 수식과 계산 능력을 길러요.
+기후변화와 지속가능한 세계: 기후 위기 대응이 일의 목적이라 → 지속가능한 발전을 탐구해요.
+생태와 환경: 환경 영향을 판단해야 해서 → 생태계와 환경 문제를 배워요.
+기후변화와 환경생태: 기후 변화의 과학적 원리를 알아야 해서 → 기후와 생태계 변화를 탐구해요.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -70709,6 +71314,17 @@
           <t>문학과 영상, 삶과 종교</t>
         </is>
       </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>무대 위에서 인물을 연기하거나 공연을 연출·기획하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>문학과 영상: 희곡과 이야기를 해석해 표현해야 해서 → 서사와 영상 표현을 배워요.
+삶과 종교: 다양한 인물의 삶과 가치관을 이해해야 해서 → 여러 삶과 신념을 탐구해요.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -70721,6 +71337,20 @@
           <t>대수, 수학과 문화, 음악, 음악 감상과 비평, 음악과 미디어</t>
         </is>
       </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>음악을 만들고 녹음·믹싱 등 소리를 다듬는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>대수: 소리의 주파수와 비율을 다루므로 → 수식과 함수 계산을 익혀요.
+수학과 문화: 화음·음계에 수학 원리가 숨어 있어서 → 음악 속 수학을 탐구해요.
+음악: 작곡의 기초 지식이 필요해서 → 음악 이론과 창작을 배워요.
+음악 감상과 비평: 좋은 음악을 분석하는 귀를 길러야 해서 → 감상과 비평을 해요.
+음악과 미디어: 디지털 장비로 작업하므로 → 미디어를 활용한 음악 제작을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -70733,6 +71363,31 @@
           <t>화법과 언어, 독서와 작문, 문학, 문학과 영상, 독서 토론과 글쓰기, 영어Ⅱ, 영미 문학 읽기, 미디어 영어, 세계사, 현대사회와 윤리, 동아시아 역사 기행, 역사로 탐구하는 현대 세계, 기후변화와 지속가능한 세계, 인간과 철학, 제2외국어 및 한문 과목 전반</t>
         </is>
       </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>이야기와 시, 수필을 써서 독자에게 생각과 감동을 전하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어: 정확하고 아름다운 문장을 쓰려면 → 국어의 규칙과 표현을 배워요.
+독서와 작문: 읽기와 쓰기가 작가의 기본기라 → 글의 구조와 쓰기 전략을 배워요.
+문학: 좋은 작품에서 배워야 해서 → 문학 작품을 깊이 감상해요.
+문학과 영상: 작품이 영화·드라마로 만들어지기도 해서 → 문학과 영상의 관계를 배워요.
+독서 토론과 글쓰기: 생각을 다듬고 표현하는 연습이 필요해서 → 토론과 글쓰기를 해요.
+영어Ⅱ: 해외 작품과 독자를 만나기 위해 → 영어 의사소통을 넓혀요.
+영미 문학 읽기: 세계 문학의 흐름을 알아야 해서 → 영어권 문학을 읽어요.
+미디어 영어: 해외 콘텐츠의 흐름을 파악하도록 → 영어 미디어를 이해해요.
+세계사: 역사는 이야기의 큰 소재라 → 세계사를 배워요.
+현대사회와 윤리: 사회와 인간에 대한 성찰이 작품의 깊이가 돼서 → 현대 윤리를 생각해요.
+동아시아 역사 기행: 역사 소설·배경 취재에 도움이 돼서 → 동아시아 역사를 탐구해요.
+역사로 탐구하는 현대 세계: 시대 배경을 생생하게 그리도록 → 현대 세계의 흐름을 탐구해요.
+기후변화와 지속가능한 세계: 환경은 요즘 문학의 중요한 주제라 → 지속가능성을 탐구해요.
+인간과 철학: 인간과 삶에 대한 질문을 깊게 하려고 → 철학적 사고를 길러요.
+제2외국어: 다른 문화의 시각을 작품에 담을 수 있도록 → 외국어와 문화를 배워요.
+한문: 고전과 한자어 표현을 풍부하게 쓰도록 → 한문을 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -70745,6 +71400,21 @@
           <t>대수, 미적분 I, 미적분 II, 기하, 전자기와 양자, 융합과학 탐구</t>
         </is>
       </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>전기·전자 회로와 반도체, 통신 장비를 설계하고 개발하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>대수: 회로 계산의 기본이라 → 수식과 함수 계산 능력을 길러요.
+미적분 I: 전류·신호의 변화를 다뤄야 해서 → 미분·적분의 기초를 배워요.
+미적분 II: 전자기 현상을 계산하려면 → 심화 미적분을 배워요.
+기하: 전기장·자기장은 벡터로 나타내서 → 벡터와 공간을 배워요.
+전자기와 양자: 반도체·전자기기의 원리라서 → 전자기와 양자 물리를 배워요.
+융합과학 탐구: 여러 기술이 합쳐진 제품을 만들므로 → 융합적 탐구를 경험해요.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -70757,6 +71427,17 @@
           <t>화법과 언어, 정치</t>
         </is>
       </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>국민의 뜻을 모아 정책과 법을 만들거나, 정치 현상을 연구하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>화법과 언어: 연설과 토론으로 사람들을 설득해야 해서 → 설득적 말하기를 배워요.
+정치: 정치 제도와 과정이 일의 중심이라 → 민주주의와 정부를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -70769,6 +71450,23 @@
           <t>주제 탐구 독서, 언어생활 탐구, 세계사, 현대사회와 윤리, 윤리와 사상, 인문학과 윤리, 인간과 철학, 논리와 사고</t>
         </is>
       </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>인간과 세계에 대한 근본 질문을 탐구하고 사상과 문헌을 연구하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>주제 탐구 독서: 고전과 연구 문헌을 깊이 읽어야 해서 → 주제 중심 독서를 해요.
+언어생활 탐구: 사상은 언어로 표현되므로 → 언어의 의미와 쓰임을 탐구해요.
+세계사: 사상은 시대 속에서 생겨나서 → 세계사의 흐름을 이해해요.
+현대사회와 윤리: 오늘의 윤리 문제를 다루므로 → 현대 사회의 윤리를 배워요.
+윤리와 사상: 동서양 사상이 연구의 기초라 → 윤리 사상을 체계적으로 배워요.
+인문학과 윤리: 인문학적 성찰을 깊게 하도록 → 인문학과 윤리를 배워요.
+인간과 철학: 철학적 질문을 던지는 연습이 필요해서 → 철학의 주요 문제를 배워요.
+논리와 사고: 주장을 엄밀하게 따져야 해서 → 논리학과 비판적 사고를 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -70781,6 +71479,20 @@
           <t>대수, 확률과 통계, 융합과학 탐구, 지구과학, 행성우주과학</t>
         </is>
       </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>우주와 천체를 관측·연구하거나 날씨와 기후를 분석해 예측하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>대수: 관측 자료를 수식으로 다루므로 → 계산과 함수의 기초를 길러요.
+확률과 통계: 일기예보는 확률과 통계로 이루어져서 → 확률과 자료 분석을 배워요.
+융합과학 탐구: 여러 과학을 함께 써서 → 탐구 설계와 자료 분석을 경험해요.
+지구과학: 대기·해양·천체가 연구 대상이라 → 지구와 우주의 기초를 배워요.
+행성우주과학: 천문 연구의 핵심 내용이라 → 행성과 우주를 깊이 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -70793,6 +71505,22 @@
           <t>체육1, 체육2, 운동과 건강, 스포츠 문화, 스포츠 과학, 스포츠 생활1, 스포츠 생활2</t>
         </is>
       </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>선수와 일반인의 운동 능력을 키우고 건강하게 운동하도록 지도하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>체육1: 다양한 운동의 기본기를 익혀야 해서 → 기초 체력과 운동 기능을 길러요.
+체육2: 여러 종목을 지도하려면 → 운동 기능과 경기 방법을 넓혀요.
+운동과 건강: 건강한 운동 처방이 핵심이라 → 운동과 건강의 원리를 배워요.
+스포츠 문화: 스포츠의 가치와 문화를 이해해야 해서 → 스포츠 문화를 탐구해요.
+스포츠 과학: 과학적인 훈련이 필요해서 → 운동을 과학적으로 분석해요.
+스포츠 생활1: 꾸준한 운동 실천이 기본이라 → 생활 속 스포츠를 경험해요.
+스포츠 생활2: 다양한 종목 경험이 지도에 도움이 돼서 → 생활 스포츠를 넓혀요.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -70805,6 +71533,22 @@
           <t>대수, 미적분 I, 확률과 통계, 미적분 II, 직무 수학, 수학과 문화, 실용 통계</t>
         </is>
       </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>자료를 수집·분석해 사회와 경제의 모습을 숫자로 보여 주는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>대수: 자료를 수식으로 다루는 기본이라 → 수식과 함수 계산을 길러요.
+미적분 I: 확률 분포를 이해하는 데 필요해서 → 미분·적분의 기초를 배워요.
+확률과 통계: 통계학의 핵심 내용이라 → 확률·분포·추정을 배워요.
+미적분 II: 고급 통계 이론을 이해하려면 → 심화 미적분을 배워요.
+직무 수학: 실제 통계 업무에 쓰이므로 → 실무 수학과 자료 해석을 배워요.
+수학과 문화: 통계가 사회에서 어떻게 쓰이는지 알도록 → 생활 속 수학을 탐구해요.
+실용 통계: 자료를 직접 모으고 분석해 보는 경험이 필요해서 → 실제 통계 프로젝트를 해요.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -70817,6 +71561,19 @@
           <t>대수, 기하, 물리학, 역학과 에너지</t>
         </is>
       </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>비행기·인공위성·로켓을 설계하고 개발하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>대수: 설계 계산의 기본이라 → 수식과 함수 계산 능력을 길러요.
+기하: 비행 궤도와 기체 모양을 다뤄야 해서 → 벡터와 공간도형을 배워요.
+물리학: 비행은 힘과 운동의 법칙으로 이루어져서 → 역학의 기초를 배워요.
+역학과 에너지: 궤도·추진력·에너지를 계산해야 해서 → 역학과 에너지를 깊이 배워요.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -70827,6 +71584,22 @@
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>대수, 미적분 I, 미적분 II, 화학, 물질과 에너지, 화학 반응의 세계, 융합과학 탐구</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>새로운 소재와 화학 제품을 개발하고 대량 생산 공정을 설계하는 일을 해요.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>대수: 공정 계산의 기본이라 → 수식과 함수 계산 능력을 길러요.
+미적분 I: 반응 속도처럼 변화를 다뤄야 해서 → 미분·적분의 기초를 배워요.
+미적분 II: 복잡한 공정 모델을 계산하려면 → 심화 미적분을 배워요.
+화학: 물질을 다루는 일의 기초라 → 물질의 구조와 반응을 배워요.
+물질과 에너지: 소재의 성질은 구조와 에너지로 결정돼서 → 물질의 상태와 에너지를 배워요.
+화학 반응의 세계: 새 물질은 화학 반응으로 만들어져서 → 다양한 반응을 깊이 배워요.
+융합과학 탐구: 신소재 연구는 여러 과학이 함께 쓰여서 → 융합적 탐구를 경험해요.</t>
         </is>
       </c>
     </row>
